--- a/outputs/evaluation/requirement/validation/gemini-3-1-flash-lite/CF_M09/first/CF_M09_req_eval.xlsx
+++ b/outputs/evaluation/requirement/validation/gemini-3-1-flash-lite/CF_M09/first/CF_M09_req_eval.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -546,6 +551,9 @@
         <v>0.2833</v>
       </c>
       <c r="D13" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="E13" t="n">
         <v>0.9172</v>
       </c>
     </row>
@@ -755,10 +763,6 @@
           <t>The system shall allow the SAT user to delete assets from a spot.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>FR</t>
@@ -772,10 +776,6 @@
           <t>Remove assets from a spot</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -806,10 +806,6 @@
           <t>The system shall allow the SAT user to create new spots in a location.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>FR</t>
@@ -823,10 +819,6 @@
           <t>Create new spots in a location</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -857,14 +849,11 @@
           <t>The system shall automatically assign the floor or allow creating new ones.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -878,14 +867,11 @@
           <t>The plant is automatically assigned or new ones can be created</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>CF_M09_R01</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -916,10 +902,6 @@
           <t>The system shall allow the SAT user to create assets assigned to a spot.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>FR</t>
@@ -933,10 +915,6 @@
           <t>Create assets assigned to a spot</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -967,14 +945,11 @@
           <t>The system shall allow assigning a name to each spot.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -988,14 +963,11 @@
           <t>Each spot can be assigned a name.</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>CF_M09_R01</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1031,9 +1003,6 @@
           <t>C_02</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1057,8 +1026,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1089,14 +1056,11 @@
           <t>The system shall automatically assign the spot, while allowing the user to decide which spot to assign.</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>R_08</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1110,14 +1074,11 @@
           <t>The spot is automatically assigned, although you can decide which spot you want to assign</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>CF_M09_R08</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1148,14 +1109,11 @@
           <t>The system shall automatically remove the spot from the list upon deletion.</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>R_05</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1169,14 +1127,11 @@
           <t>The spot is automatically removed from the list.</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>CF_M09_R05</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1207,14 +1162,11 @@
           <t>The system shall prevent the deletion of a spot if it has assigned assets.</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>R_05</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1228,14 +1180,11 @@
           <t>A spot cannot be deleted if it has assets assigned to it.</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>CF_M09_R05</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1266,14 +1215,11 @@
           <t>The system shall allow adding all asset and asset-type attributes to the asset.</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>R_08</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1287,14 +1233,11 @@
           <t>All asset and asset type attributes can be added to the asset.</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>CF_M09_R08</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1325,14 +1268,11 @@
           <t>The system shall allow leaving the serial number blank, to be assigned during installation.</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>R_08</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1346,14 +1286,11 @@
           <t>The serial number can be left blank, in which case it will be assigned during installation.</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>CF_M09_R08</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1384,14 +1321,11 @@
           <t>The system shall display the created spot automatically.</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>R_01</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1405,14 +1339,11 @@
           <t>The created spot is automatically displayed.</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>CF_M09_R01</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1443,14 +1374,11 @@
           <t>All colors used in the interface must correspond to those defined in the Waapiti color palette included in the platform code.</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>R_15</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1464,14 +1392,11 @@
           <t>All colors used in the interface correspond to those defined in the Waapiti color palette included in the platform code.</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>CF_M09_R42</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1502,14 +1427,11 @@
           <t>The system shall automatically remove the asset from the list.</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1523,14 +1445,11 @@
           <t>The asset is automatically removed from the list.</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>CF_M09_R12</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1561,14 +1480,11 @@
           <t>The system shall only allow deleting an asset if it is not assigned to an intervention.</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>R_12</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1582,14 +1498,11 @@
           <t>An asset can only be deleted if it is not assigned to an intervention.</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>CF_M09_R12</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1625,9 +1538,6 @@
           <t>C_01</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>QR</t>
@@ -1651,8 +1561,6 @@
           <t>Volere</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1683,14 +1591,11 @@
           <t>The system responds to any user action in less than five seconds.</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>R_17</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>criterion</t>
@@ -1704,14 +1609,11 @@
           <t>The system responds to any user action in less than five seconds.</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>CF_M09_R48</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
